--- a/output/C.xlsx
+++ b/output/C.xlsx
@@ -413,196 +413,271 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:BA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>(A)거래처코드</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>(A)거래처명</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(A)시도명</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(A)시군구명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>(A)도로명주소</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>(A)전화번호</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>(A)고객코드</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>(A)고객명</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>(A)진료과목명</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>(B)거래처코드</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>(B)거래처명</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>(B)시도명</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>(B)시군구명</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>(B)도로명주소</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>(B)전화번호</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>(B)고객코드</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>(B)고객명</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>(B)진료과목명</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>거래처 기본 유사도점수</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>고객명 가점</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>거래처 최종 유사도점수</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>거래처 일치여부</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>고객명 일치여부</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>근접후보1_(B)거래처코드</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>근접후보1_(B)거래처명</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>근접후보1_(B)시도명</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>근접후보1_(B)시군구명</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>근접후보1_(B)도로명주소</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>근접후보1_(B)전화번호</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>근접후보1_(B)고객코드</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>근접후보1_(B)고객명</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>근접후보1_(B)진료과목명</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>근접후보1_거래처 최종 유사도점수</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>근접후보2_(B)거래처코드</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>근접후보2_(B)거래처명</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>근접후보2_(B)시도명</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>근접후보2_(B)시군구명</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>근접후보2_(B)도로명주소</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>근접후보2_(B)전화번호</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>근접후보2_(B)고객코드</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
         <is>
           <t>근접후보2_(B)고객명</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>근접후보2_(B)진료과목명</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>근접후보2_거래처 최종 유사도점수</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>근접후보3_(B)거래처코드</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>근접후보3_(B)거래처명</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>근접후보3_(B)시도명</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>근접후보3_(B)시군구명</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>근접후보3_(B)도로명주소</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>근접후보3_(B)전화번호</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>근접후보3_(B)고객코드</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>근접후보3_(B)고객명</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>근접후보3_(B)진료과목명</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
         <is>
           <t>근접후보3_거래처 최종 유사도점수</t>
         </is>
@@ -611,89 +686,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>가톨릭대학교서울성모병원</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>서울특별시</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>서대문구</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>서울특별시 서대문구 연세로 50-1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>02-1234-5678</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>홍길동</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>내과</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>학교법인가톨릭학원가톨릭대학교서울성모병원</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>서대문구</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>서울특별시서대문구연세로501</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0212345678</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>D001</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>홍길동</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>내과</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
         <v>100</v>
       </c>
-      <c r="N2" t="n">
+      <c r="T2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
+      <c r="U2" t="n">
         <v>100</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>매칭</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
@@ -709,134 +808,200 @@
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>ABC병원</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>경기도</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>수원시</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>경기도 수원시 영통구</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>031-1899-9542</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>C002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>김철수</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>정형외과</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>ABC병원</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>수원시</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>경기도수원시영통구</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>031-1899-9542</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>D003</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>김철수</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>정형외과</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
         <v>100</v>
       </c>
-      <c r="N3" t="n">
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
+      <c r="U3" t="n">
         <v>100</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>매칭</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>ABC병원</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>경기</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>수원시</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>경기도수원시영통구</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1899-9542</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>D002</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>이영희</t>
         </is>
       </c>
-      <c r="X3" t="n">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>피부과</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>100</v>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
